--- a/docs/data_excel/260617/통합_엑셀_템플릿_legacy변환_260625_1504.xlsx
+++ b/docs/data_excel/260617/통합_엑셀_템플릿_legacy변환_260625_1504.xlsx
@@ -8,16 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mycho\Downloads\_Licentia\Coding\pmo-ops-portal\docs\data_excel\260617\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34445765-19C4-4DA3-A6DD-2725C87ADB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31FCCC6-745F-4DFF-A875-79F80DFD9F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16350" yWindow="-16215" windowWidth="26280" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="375" windowWidth="26280" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="프로젝트관리" sheetId="1" r:id="rId1"/>
     <sheet name="인력관리" sheetId="2" r:id="rId2"/>
     <sheet name="프로젝트배정" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -7955,80 +7968,80 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:25" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+    <row r="61" spans="1:25" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="18" t="s">
         <v>304</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="18" t="s">
         <v>305</v>
       </c>
-      <c r="G61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H61" s="14" t="s">
+      <c r="G61" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="I61" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="J61" s="14" t="s">
+      <c r="J61" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="K61" s="14" t="s">
+      <c r="K61" s="18" t="s">
         <v>307</v>
       </c>
-      <c r="L61" s="14" t="s">
+      <c r="L61" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="M61" s="14" t="s">
+      <c r="M61" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="N61" s="14" t="s">
+      <c r="N61" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="O61" s="14" t="s">
+      <c r="O61" s="18" t="s">
         <v>309</v>
       </c>
-      <c r="P61" s="14" t="s">
+      <c r="P61" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="Q61" s="14" t="s">
+      <c r="Q61" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="R61" s="14" t="s">
+      <c r="R61" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="S61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="T61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="U61" s="14" t="s">
+      <c r="S61" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="T61" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="U61" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="V61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="W61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y61" s="14" t="s">
+      <c r="V61" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="W61" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="X61" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y61" s="18" t="s">
         <v>39</v>
       </c>
     </row>
